--- a/transactions/Recap_transaction_fonciere_appel_de_fonds.xlsx
+++ b/transactions/Recap_transaction_fonciere_appel_de_fonds.xlsx
@@ -156,7 +156,12 @@
     </comment>
     <comment ref="B13" authorId="0" shapeId="0">
       <text>
-        <t>Frais de notaire calcules sur le prix client (prix avec commission). Hypothese : 6% indique par l'agent.</t>
+        <t>Taxes gouvernementales : 5% du prix client (prix avec commission). Hypothese indiquee par l'agent.</t>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0">
+      <text>
+        <t>Honoraires du notaire : 1% du prix client (prix avec commission). Hypothese indiquee par l'agent.</t>
       </text>
     </comment>
   </commentList>
@@ -452,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -562,103 +567,86 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Taux frais de notaire</t>
+          <t>Taxes gouvernementales (% du prix client)</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Frais de geometre (EUR)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>1000</v>
+          <t>Honoraires du notaire (% du prix client)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>Frais de geometre (EUR)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>Taux d'acompte (appel de fonds)</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B16" s="5" t="n">
         <v>0.1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>DETAIL DU CALCUL</t>
-        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
+          <t>DETAIL DU CALCUL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>Surface (ares)</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>Duree (ans)</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D19" s="1" t="inlineStr">
         <is>
           <t>Prix unitaire (IDR/are/an)</t>
         </is>
       </c>
-      <c r="E18" s="1" t="inlineStr">
+      <c r="E19" s="1" t="inlineStr">
         <is>
           <t>Montant IDR</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F19" s="1" t="inlineStr">
         <is>
           <t>Montant EUR</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Prix du terrain - PRIX VENDEUR</t>
-        </is>
-      </c>
-      <c r="B19" s="3">
-        <f>B7</f>
-        <v/>
-      </c>
-      <c r="C19" s="4">
-        <f>B9</f>
-        <v/>
-      </c>
-      <c r="D19" s="4">
-        <f>B10</f>
-        <v/>
-      </c>
-      <c r="E19" s="4">
-        <f>B19*C19*D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="3">
-        <f>E19/$B$12</f>
-        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Prix du terrain - PRIX CLIENT (avec commission)</t>
+          <t>Prix du terrain - PRIX VENDEUR</t>
         </is>
       </c>
       <c r="B20" s="3">
@@ -670,7 +658,7 @@
         <v/>
       </c>
       <c r="D20" s="4">
-        <f>B11</f>
+        <f>B10</f>
         <v/>
       </c>
       <c r="E20" s="4">
@@ -685,11 +673,23 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>dont commission agence (ecart vendeur / client)</t>
-        </is>
+          <t>Prix du terrain - PRIX CLIENT (avec commission)</t>
+        </is>
+      </c>
+      <c r="B21" s="3">
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="C21" s="4">
+        <f>B9</f>
+        <v/>
+      </c>
+      <c r="D21" s="4">
+        <f>B11</f>
+        <v/>
       </c>
       <c r="E21" s="4">
-        <f>E20-E19</f>
+        <f>B21*C21*D21</f>
         <v/>
       </c>
       <c r="F21" s="3">
@@ -697,81 +697,108 @@
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>dont commission agence (ecart vendeur / client)</t>
+        </is>
+      </c>
+      <c r="E22" s="4">
+        <f>E21-E20</f>
+        <v/>
+      </c>
+      <c r="F22" s="3">
+        <f>E22/$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>FRAIS ANNEXES</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Frais de notaire (6% du prix client)</t>
-        </is>
-      </c>
-      <c r="D24" s="5">
-        <f>B13</f>
-        <v/>
-      </c>
-      <c r="E24" s="4">
-        <f>E20*$B$13</f>
-        <v/>
-      </c>
-      <c r="F24" s="3">
-        <f>E24/$B$12</f>
-        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>Taxes gouvernementales (5% du prix client)</t>
+        </is>
+      </c>
+      <c r="D25" s="5">
+        <f>B13</f>
+        <v/>
+      </c>
+      <c r="E25" s="4">
+        <f>E21*$B$13</f>
+        <v/>
+      </c>
+      <c r="F25" s="3">
+        <f>E25/$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Honoraires du notaire (1% du prix client)</t>
+        </is>
+      </c>
+      <c r="D26" s="5">
+        <f>B14</f>
+        <v/>
+      </c>
+      <c r="E26" s="4">
+        <f>E21*$B$14</f>
+        <v/>
+      </c>
+      <c r="F26" s="3">
+        <f>E26/$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Sous-total frais de notaire (taxes + honoraires)</t>
+        </is>
+      </c>
+      <c r="D27" s="5">
+        <f>B13+B14</f>
+        <v/>
+      </c>
+      <c r="E27" s="4">
+        <f>E25+E26</f>
+        <v/>
+      </c>
+      <c r="F27" s="3">
+        <f>E27/$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>Frais de geometre (forfait 1 000 EUR)</t>
         </is>
       </c>
-      <c r="E25" s="4">
-        <f>$B$14*$B$12</f>
-        <v/>
-      </c>
-      <c r="F25" s="3">
-        <f>$B$14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="E28" s="4">
+        <f>$B$15*$B$12</f>
+        <v/>
+      </c>
+      <c r="F28" s="3">
+        <f>$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>TOTAL DE L'OPERATION POUR L'ACHETEUR</t>
         </is>
       </c>
-      <c r="E27" s="6">
-        <f>E20+E24+E25</f>
-        <v/>
-      </c>
-      <c r="F27" s="7">
-        <f>E27/$B$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>APPEL DE FONDS</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Acompte 10% du total de l'operation (reservation notaire)</t>
-        </is>
-      </c>
-      <c r="D30" s="5">
-        <f>B15</f>
-        <v/>
-      </c>
       <c r="E30" s="6">
-        <f>E27*$B$15</f>
+        <f>E21+E27+E28</f>
         <v/>
       </c>
       <c r="F30" s="7">
@@ -779,75 +806,108 @@
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Solde a regler apres acompte</t>
-        </is>
-      </c>
-      <c r="E31" s="4">
-        <f>E27-E30</f>
-        <v/>
-      </c>
-      <c r="F31" s="3">
-        <f>E31/$B$12</f>
-        <v/>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>APPEL DE FONDS</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Pour information : 10% du prix du terrain seul</t>
-        </is>
-      </c>
-      <c r="E33" s="4">
-        <f>E20*$B$15</f>
-        <v/>
-      </c>
-      <c r="F33" s="3">
+          <t>Acompte 10% du total de l'operation (reservation notaire)</t>
+        </is>
+      </c>
+      <c r="D33" s="5">
+        <f>B16</f>
+        <v/>
+      </c>
+      <c r="E33" s="6">
+        <f>E30*$B$16</f>
+        <v/>
+      </c>
+      <c r="F33" s="7">
         <f>E33/$B$12</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>NOTES / HYPOTHESES</t>
-        </is>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Solde a regler apres acompte</t>
+        </is>
+      </c>
+      <c r="E34" s="4">
+        <f>E30-E33</f>
+        <v/>
+      </c>
+      <c r="F34" s="3">
+        <f>E34/$B$12</f>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1 are = 100 m2 -&gt; terrain de 600 m2. Prix leasehold exprime en IDR par are et par an, sur 30 ans.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Taux de change en B12 : reference BCE du 20/08/2026 (1 EUR = 20 788,62 IDR). A actualiser avant envoi au client.</t>
-        </is>
+          <t>Pour information : 10% du prix du terrain seul</t>
+        </is>
+      </c>
+      <c r="E36" s="4">
+        <f>E21*$B$16</f>
+        <v/>
+      </c>
+      <c r="F36" s="3">
+        <f>E36/$B$12</f>
+        <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Frais de notaire (B13) calcules sur le prix client avec commission. Modifier la formule en E24 si la base retenue est le prix vendeur.</t>
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>NOTES / HYPOTHESES</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Frais de geometre saisis en EUR (B14) et convertis en IDR au taux B12.</t>
+          <t>1 are = 100 m2 -&gt; terrain de 600 m2. Prix leasehold exprime en IDR par are et par an, sur 30 ans.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Seules les cellules de parametres (colonne B, lignes 7 a 15) sont a saisir : tout le reste du tableau est calcule par formules et se met a jour automatiquement.</t>
+          <t>Taux de change en B12 : reference BCE du 20/08/2026 (1 EUR = 20 788,62 IDR). A actualiser avant envoi au client.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Frais de notaire detailles : 5% de taxes gouvernementales (B13) + 1% d'honoraires du notaire (B14), soit 6% au total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ces deux taux sont appliques au prix client avec commission. Remplacer E21 par E20 dans les formules E25 et E26 si la base retenue est le prix vendeur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Frais de geometre saisis en EUR (B15) et convertis en IDR au taux B12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Seules les cellules de parametres (colonne B, lignes 7 a 16) sont a saisir : tout le reste du tableau est calcule par formules et se met a jour automatiquement.</t>
         </is>
       </c>
     </row>

--- a/transactions/Recap_transaction_fonciere_appel_de_fonds.xlsx
+++ b/transactions/Recap_transaction_fonciere_appel_de_fonds.xlsx
@@ -164,6 +164,17 @@
         <t>Honoraires du notaire : 1% du prix client (prix avec commission). Hypothese indiquee par l'agent.</t>
       </text>
     </comment>
+    <comment ref="B15" authorId="0" shapeId="0">
+      <text>
+        <t>Forfait plancher : si 1% du prix client donne moins de 10 000 000 IDR, ce forfait s'applique a la place du pourcentage.</t>
+      </text>
+    </comment>
+    <comment ref="E27" authorId="0" shapeId="0">
+      <text>
+        <t>MAX entre 1% du prix client et le forfait minimum de la cellule B15 : si le pourcentage donne moins de 10 000 000 IDR, c'est le forfait qui s'applique.
+La colonne D affiche le taux reellement supporte.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -457,10 +468,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
@@ -587,93 +598,76 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Frais de geometre (EUR)</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>1000</v>
+          <t>Honoraires du notaire - forfait minimum (IDR)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>10000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>Frais de geometre (EUR)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>Taux d'acompte (appel de fonds)</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B17" s="5" t="n">
         <v>0.1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>DETAIL DU CALCUL</t>
-        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
+          <t>DETAIL DU CALCUL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>Surface (ares)</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>Duree (ans)</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D20" s="1" t="inlineStr">
         <is>
           <t>Prix unitaire (IDR/are/an)</t>
         </is>
       </c>
-      <c r="E19" s="1" t="inlineStr">
+      <c r="E20" s="1" t="inlineStr">
         <is>
           <t>Montant IDR</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="F20" s="1" t="inlineStr">
         <is>
           <t>Montant EUR</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Prix du terrain - PRIX VENDEUR</t>
-        </is>
-      </c>
-      <c r="B20" s="3">
-        <f>B7</f>
-        <v/>
-      </c>
-      <c r="C20" s="4">
-        <f>B9</f>
-        <v/>
-      </c>
-      <c r="D20" s="4">
-        <f>B10</f>
-        <v/>
-      </c>
-      <c r="E20" s="4">
-        <f>B20*C20*D20</f>
-        <v/>
-      </c>
-      <c r="F20" s="3">
-        <f>E20/$B$12</f>
-        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Prix du terrain - PRIX CLIENT (avec commission)</t>
+          <t>Prix du terrain - PRIX VENDEUR</t>
         </is>
       </c>
       <c r="B21" s="3">
@@ -685,7 +679,7 @@
         <v/>
       </c>
       <c r="D21" s="4">
-        <f>B11</f>
+        <f>B10</f>
         <v/>
       </c>
       <c r="E21" s="4">
@@ -700,11 +694,23 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>dont commission agence (ecart vendeur / client)</t>
-        </is>
+          <t>Prix du terrain - PRIX CLIENT (avec commission)</t>
+        </is>
+      </c>
+      <c r="B22" s="3">
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="C22" s="4">
+        <f>B9</f>
+        <v/>
+      </c>
+      <c r="D22" s="4">
+        <f>B11</f>
+        <v/>
       </c>
       <c r="E22" s="4">
-        <f>E21-E20</f>
+        <f>B22*C22*D22</f>
         <v/>
       </c>
       <c r="F22" s="3">
@@ -712,44 +718,40 @@
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>dont commission agence (ecart vendeur / client)</t>
+        </is>
+      </c>
+      <c r="E23" s="4">
+        <f>E22-E21</f>
+        <v/>
+      </c>
+      <c r="F23" s="3">
+        <f>E23/$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>FRAIS ANNEXES</t>
         </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Taxes gouvernementales (5% du prix client)</t>
-        </is>
-      </c>
-      <c r="D25" s="5">
-        <f>B13</f>
-        <v/>
-      </c>
-      <c r="E25" s="4">
-        <f>E21*$B$13</f>
-        <v/>
-      </c>
-      <c r="F25" s="3">
-        <f>E25/$B$12</f>
-        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Honoraires du notaire (1% du prix client)</t>
+          <t>Taxes gouvernementales (5% du prix client)</t>
         </is>
       </c>
       <c r="D26" s="5">
-        <f>B14</f>
+        <f>B13</f>
         <v/>
       </c>
       <c r="E26" s="4">
-        <f>E21*$B$14</f>
+        <f>E22*$B$13</f>
         <v/>
       </c>
       <c r="F26" s="3">
@@ -760,15 +762,15 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Sous-total frais de notaire (taxes + honoraires)</t>
+          <t>Honoraires du notaire (1% du prix client, minimum 10 000 000 IDR)</t>
         </is>
       </c>
       <c r="D27" s="5">
-        <f>B13+B14</f>
+        <f>IF(E22=0,0,E27/E22)</f>
         <v/>
       </c>
       <c r="E27" s="4">
-        <f>E25+E26</f>
+        <f>MAX(E22*$B$14,$B$15)</f>
         <v/>
       </c>
       <c r="F27" s="3">
@@ -779,135 +781,161 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>Sous-total frais de notaire (taxes + honoraires)</t>
+        </is>
+      </c>
+      <c r="D28" s="5">
+        <f>IF(E22=0,0,E28/E22)</f>
+        <v/>
+      </c>
+      <c r="E28" s="4">
+        <f>E26+E27</f>
+        <v/>
+      </c>
+      <c r="F28" s="3">
+        <f>E28/$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>Frais de geometre (forfait 1 000 EUR)</t>
         </is>
       </c>
-      <c r="E28" s="4">
-        <f>$B$15*$B$12</f>
-        <v/>
-      </c>
-      <c r="F28" s="3">
-        <f>$B$15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="E29" s="4">
+        <f>$B$16*$B$12</f>
+        <v/>
+      </c>
+      <c r="F29" s="3">
+        <f>$B$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>TOTAL DE L'OPERATION POUR L'ACHETEUR</t>
         </is>
       </c>
-      <c r="E30" s="6">
-        <f>E21+E27+E28</f>
-        <v/>
-      </c>
-      <c r="F30" s="7">
-        <f>E30/$B$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="E31" s="6">
+        <f>E22+E28+E29</f>
+        <v/>
+      </c>
+      <c r="F31" s="7">
+        <f>E31/$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>APPEL DE FONDS</t>
         </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Acompte 10% du total de l'operation (reservation notaire)</t>
-        </is>
-      </c>
-      <c r="D33" s="5">
-        <f>B16</f>
-        <v/>
-      </c>
-      <c r="E33" s="6">
-        <f>E30*$B$16</f>
-        <v/>
-      </c>
-      <c r="F33" s="7">
-        <f>E33/$B$12</f>
-        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>Acompte 10% du total de l'operation (reservation notaire)</t>
+        </is>
+      </c>
+      <c r="D34" s="5">
+        <f>B17</f>
+        <v/>
+      </c>
+      <c r="E34" s="6">
+        <f>E31*$B$17</f>
+        <v/>
+      </c>
+      <c r="F34" s="7">
+        <f>E34/$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
           <t>Solde a regler apres acompte</t>
         </is>
       </c>
-      <c r="E34" s="4">
-        <f>E30-E33</f>
-        <v/>
-      </c>
-      <c r="F34" s="3">
-        <f>E34/$B$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="E35" s="4">
+        <f>E31-E34</f>
+        <v/>
+      </c>
+      <c r="F35" s="3">
+        <f>E35/$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Pour information : 10% du prix du terrain seul</t>
         </is>
       </c>
-      <c r="E36" s="4">
-        <f>E21*$B$16</f>
-        <v/>
-      </c>
-      <c r="F36" s="3">
-        <f>E36/$B$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="E37" s="4">
+        <f>E22*$B$17</f>
+        <v/>
+      </c>
+      <c r="F37" s="3">
+        <f>E37/$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>NOTES / HYPOTHESES</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>1 are = 100 m2 -&gt; terrain de 600 m2. Prix leasehold exprime en IDR par are et par an, sur 30 ans.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Taux de change en B12 : reference BCE du 20/08/2026 (1 EUR = 20 788,62 IDR). A actualiser avant envoi au client.</t>
+          <t>1 are = 100 m2 -&gt; terrain de 600 m2. Prix leasehold exprime en IDR par are et par an, sur 30 ans.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Frais de notaire detailles : 5% de taxes gouvernementales (B13) + 1% d'honoraires du notaire (B14), soit 6% au total.</t>
+          <t>Taux de change en B12 : reference BCE du 20/08/2026 (1 EUR = 20 788,62 IDR). A actualiser avant envoi au client.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Ces deux taux sont appliques au prix client avec commission. Remplacer E21 par E20 dans les formules E25 et E26 si la base retenue est le prix vendeur.</t>
+          <t>Frais de notaire detailles : taxes gouvernementales 5% (B13) + honoraires du notaire 1% (B14).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Frais de geometre saisis en EUR (B15) et convertis en IDR au taux B12.</t>
+          <t>Honoraires du notaire : le pourcentage s'applique sauf s'il donne moins que le forfait minimum de 10 000 000 IDR (B15), auquel cas le forfait est retenu (formule MAX en E27).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Seules les cellules de parametres (colonne B, lignes 7 a 16) sont a saisir : tout le reste du tableau est calcule par formules et se met a jour automatiquement.</t>
+          <t>Ces taux sont appliques au prix client avec commission. Remplacer E22 par E21 dans les formules E26 et E27 si la base retenue est le prix vendeur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Frais de geometre saisis en EUR (B16) et convertis en IDR au taux B12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Seules les cellules de parametres (colonne B, lignes 7 a 17) sont a saisir : tout le reste du tableau est calcule par formules et se met a jour automatiquement.</t>
         </is>
       </c>
     </row>

--- a/transactions/Recap_transaction_fonciere_appel_de_fonds.xlsx
+++ b/transactions/Recap_transaction_fonciere_appel_de_fonds.xlsx
@@ -148,31 +148,31 @@
     <author>Agence</author>
   </authors>
   <commentList>
-    <comment ref="B12" authorId="0" shapeId="0">
+    <comment ref="B13" authorId="0" shapeId="0">
       <text>
         <t>Taux de reference BCE du 20/08/2026 : 1 EUR = 20 788,62 IDR (source : api.frankfurter.dev).
 A actualiser au taux du jour / au taux retenu avec le client.</t>
       </text>
     </comment>
-    <comment ref="B13" authorId="0" shapeId="0">
+    <comment ref="B14" authorId="0" shapeId="0">
       <text>
         <t>Taxes gouvernementales : 5% du prix client (prix avec commission). Hypothese indiquee par l'agent.</t>
       </text>
     </comment>
-    <comment ref="B14" authorId="0" shapeId="0">
+    <comment ref="B15" authorId="0" shapeId="0">
       <text>
         <t>Honoraires du notaire : 1% du prix client (prix avec commission). Hypothese indiquee par l'agent.</t>
       </text>
     </comment>
-    <comment ref="B15" authorId="0" shapeId="0">
+    <comment ref="B16" authorId="0" shapeId="0">
       <text>
-        <t>Forfait plancher : si 1% du prix client donne moins de 10 000 000 IDR, ce forfait s'applique a la place du pourcentage.</t>
+        <t>Forfait plancher : si le pourcentage donne moins de 10 000 000 IDR, ce forfait s'applique a la place du pourcentage.</t>
       </text>
     </comment>
-    <comment ref="E27" authorId="0" shapeId="0">
+    <comment ref="E28" authorId="0" shapeId="0">
       <text>
-        <t>MAX entre 1% du prix client et le forfait minimum de la cellule B15 : si le pourcentage donne moins de 10 000 000 IDR, c'est le forfait qui s'applique.
-La colonne D affiche le taux reellement supporte.</t>
+        <t>MAX entre le pourcentage d'honoraires et le forfait minimum : si le pourcentage donne moins de 10 000 000 IDR, c'est le forfait qui s'applique.
+La colonne des taux affiche le taux reellement supporte.</t>
       </text>
     </comment>
   </commentList>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -487,226 +487,206 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Client :</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Regime : LEASEHOLD (bail 30 ans)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Terrain / localisation :</t>
+          <t>Client :</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Terrain / localisation :</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>Date :</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>PARAMETRES (cellules a modifier)</t>
         </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Surface du terrain (ares)</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Surface du terrain (m2)</t>
-        </is>
-      </c>
-      <c r="B8" s="4">
-        <f>B7*100</f>
-        <v/>
+          <t>Surface du terrain (ares)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Duree du leasehold (annees)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>30</v>
+          <t>Surface du terrain (m2)</t>
+        </is>
+      </c>
+      <c r="B9" s="4">
+        <f>B8*100</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Prix vendeur (IDR / are / an)</t>
+          <t>Duree du leasehold (annees)</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>4000000</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Prix client avec commission (IDR / are / an)</t>
+          <t>Prix vendeur (IDR / are / an)</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Taux de change (IDR pour 1 EUR)</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>20788.62</v>
+          <t>Prix client avec commission (IDR / are / an)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>5000000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Taxes gouvernementales (% du prix client)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>0.05</v>
+          <t>Taux de change (IDR pour 1 EUR)</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>20788.62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Honoraires du notaire (% du prix client)</t>
+          <t>Taxes gouvernementales (% du prix client)</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Honoraires du notaire - forfait minimum (IDR)</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>10000000</v>
+          <t>Honoraires du notaire (% du prix client)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Frais de geometre (EUR)</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>1000</v>
+          <t>Honoraires du notaire - forfait minimum (IDR)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>10000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>Frais de geometre (EUR)</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>Taux d'acompte (appel de fonds)</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B18" s="5" t="n">
         <v>0.1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>DETAIL DU CALCUL</t>
-        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
+          <t>DETAIL DU CALCUL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>Surface (ares)</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>Duree (ans)</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>Prix unitaire (IDR/are/an)</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>Prix unitaire (IDR / are / an)</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
         <is>
           <t>Montant IDR</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>Montant EUR</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Prix du terrain - PRIX VENDEUR</t>
-        </is>
-      </c>
-      <c r="B21" s="3">
-        <f>B7</f>
-        <v/>
-      </c>
-      <c r="C21" s="4">
-        <f>B9</f>
-        <v/>
-      </c>
-      <c r="D21" s="4">
-        <f>B10</f>
-        <v/>
-      </c>
-      <c r="E21" s="4">
-        <f>B21*C21*D21</f>
-        <v/>
-      </c>
-      <c r="F21" s="3">
-        <f>E21/$B$12</f>
-        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Prix du terrain - PRIX CLIENT (avec commission)</t>
+          <t>Prix du terrain - PRIX VENDEUR</t>
         </is>
       </c>
       <c r="B22" s="3">
-        <f>B7</f>
+        <f>$B$8</f>
         <v/>
       </c>
       <c r="C22" s="4">
-        <f>B9</f>
+        <f>$B$10</f>
         <v/>
       </c>
       <c r="D22" s="4">
-        <f>B11</f>
+        <f>$B$11</f>
         <v/>
       </c>
       <c r="E22" s="4">
@@ -714,228 +694,262 @@
         <v/>
       </c>
       <c r="F22" s="3">
-        <f>E22/$B$12</f>
+        <f>E22/$B$13</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>Prix du terrain - PRIX CLIENT (avec commission)</t>
+        </is>
+      </c>
+      <c r="B23" s="3">
+        <f>$B$8</f>
+        <v/>
+      </c>
+      <c r="C23" s="4">
+        <f>$B$10</f>
+        <v/>
+      </c>
+      <c r="D23" s="4">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="E23" s="4">
+        <f>B23*C23*D23</f>
+        <v/>
+      </c>
+      <c r="F23" s="3">
+        <f>E23/$B$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>dont commission agence (ecart vendeur / client)</t>
         </is>
       </c>
-      <c r="E23" s="4">
-        <f>E22-E21</f>
-        <v/>
-      </c>
-      <c r="F23" s="3">
-        <f>E23/$B$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="E24" s="4">
+        <f>E23-E22</f>
+        <v/>
+      </c>
+      <c r="F24" s="3">
+        <f>E24/$B$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>FRAIS ANNEXES</t>
         </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Taxes gouvernementales (5% du prix client)</t>
-        </is>
-      </c>
-      <c r="D26" s="5">
-        <f>B13</f>
-        <v/>
-      </c>
-      <c r="E26" s="4">
-        <f>E22*$B$13</f>
-        <v/>
-      </c>
-      <c r="F26" s="3">
-        <f>E26/$B$12</f>
-        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Honoraires du notaire (1% du prix client, minimum 10 000 000 IDR)</t>
+          <t>Taxes gouvernementales (5% du prix client)</t>
         </is>
       </c>
       <c r="D27" s="5">
-        <f>IF(E22=0,0,E27/E22)</f>
+        <f>$B$14</f>
         <v/>
       </c>
       <c r="E27" s="4">
-        <f>MAX(E22*$B$14,$B$15)</f>
+        <f>E23*$B$14</f>
         <v/>
       </c>
       <c r="F27" s="3">
-        <f>E27/$B$12</f>
+        <f>E27/$B$13</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Sous-total frais de notaire (taxes + honoraires)</t>
+          <t>Honoraires du notaire (1% du prix client, minimum 10 000 000 IDR)</t>
         </is>
       </c>
       <c r="D28" s="5">
-        <f>IF(E22=0,0,E28/E22)</f>
+        <f>IF(E23=0,0,E28/E23)</f>
         <v/>
       </c>
       <c r="E28" s="4">
-        <f>E26+E27</f>
+        <f>MAX(E23*$B$15,$B$16)</f>
         <v/>
       </c>
       <c r="F28" s="3">
-        <f>E28/$B$12</f>
+        <f>E28/$B$13</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>Sous-total frais de notaire (taxes + honoraires)</t>
+        </is>
+      </c>
+      <c r="D29" s="5">
+        <f>IF(E23=0,0,E29/E23)</f>
+        <v/>
+      </c>
+      <c r="E29" s="4">
+        <f>E27+E28</f>
+        <v/>
+      </c>
+      <c r="F29" s="3">
+        <f>E29/$B$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>Frais de geometre (forfait 1 000 EUR)</t>
         </is>
       </c>
-      <c r="E29" s="4">
-        <f>$B$16*$B$12</f>
-        <v/>
-      </c>
-      <c r="F29" s="3">
-        <f>$B$16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="E30" s="4">
+        <f>$B$17*$B$13</f>
+        <v/>
+      </c>
+      <c r="F30" s="3">
+        <f>$B$17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>TOTAL DE L'OPERATION POUR L'ACHETEUR</t>
         </is>
       </c>
-      <c r="E31" s="6">
-        <f>E22+E28+E29</f>
-        <v/>
-      </c>
-      <c r="F31" s="7">
-        <f>E31/$B$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="E32" s="6">
+        <f>E23+E29+E30</f>
+        <v/>
+      </c>
+      <c r="F32" s="7">
+        <f>E32/$B$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>APPEL DE FONDS</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>Acompte 10% du total de l'operation (reservation notaire)</t>
         </is>
       </c>
-      <c r="D34" s="5">
-        <f>B17</f>
-        <v/>
-      </c>
-      <c r="E34" s="6">
-        <f>E31*$B$17</f>
-        <v/>
-      </c>
-      <c r="F34" s="7">
-        <f>E34/$B$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="D35" s="5">
+        <f>$B$18</f>
+        <v/>
+      </c>
+      <c r="E35" s="6">
+        <f>E32*$B$18</f>
+        <v/>
+      </c>
+      <c r="F35" s="7">
+        <f>E35/$B$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Solde a regler apres acompte</t>
         </is>
       </c>
-      <c r="E35" s="4">
-        <f>E31-E34</f>
-        <v/>
-      </c>
-      <c r="F35" s="3">
-        <f>E35/$B$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="E36" s="4">
+        <f>E32-E35</f>
+        <v/>
+      </c>
+      <c r="F36" s="3">
+        <f>E36/$B$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Pour information : 10% du prix du terrain seul</t>
         </is>
       </c>
-      <c r="E37" s="4">
-        <f>E22*$B$17</f>
-        <v/>
-      </c>
-      <c r="F37" s="3">
-        <f>E37/$B$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="E38" s="4">
+        <f>E23*$B$18</f>
+        <v/>
+      </c>
+      <c r="F38" s="3">
+        <f>E38/$B$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>NOTES / HYPOTHESES</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>1 are = 100 m2 -&gt; terrain de 600 m2. Prix leasehold exprime en IDR par are et par an, sur 30 ans.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Taux de change en B12 : reference BCE du 20/08/2026 (1 EUR = 20 788,62 IDR). A actualiser avant envoi au client.</t>
+          <t>1 are = 100 m2 -&gt; terrain de 600 m2.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Frais de notaire detailles : taxes gouvernementales 5% (B13) + honoraires du notaire 1% (B14).</t>
+          <t>Achat en LEASEHOLD : prix exprime en IDR par are et par an, multiplie par la duree du bail.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Honoraires du notaire : le pourcentage s'applique sauf s'il donne moins que le forfait minimum de 10 000 000 IDR (B15), auquel cas le forfait est retenu (formule MAX en E27).</t>
+          <t>Taux de change en B13 : reference BCE du 20/08/2026 (1 EUR = 20 788,62 IDR). A actualiser avant envoi au client.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Ces taux sont appliques au prix client avec commission. Remplacer E22 par E21 dans les formules E26 et E27 si la base retenue est le prix vendeur.</t>
+          <t>Frais de notaire detailles : taxes gouvernementales 5% (B14) + honoraires du notaire 1% (B15).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Frais de geometre saisis en EUR (B16) et convertis en IDR au taux B12.</t>
+          <t>Honoraires du notaire : le pourcentage s'applique sauf s'il donne moins que le forfait minimum de 10 000 000 IDR (B16), auquel cas le forfait est retenu (formule MAX en E28).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Seules les cellules de parametres (colonne B, lignes 7 a 17) sont a saisir : tout le reste du tableau est calcule par formules et se met a jour automatiquement.</t>
+          <t>Ces taux sont appliques au prix client avec commission. Remplacer E23 par E22 dans les formules de frais si la base retenue est le prix vendeur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Frais de geometre saisis en EUR (B17) et convertis en IDR au taux B13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Seules les cellules de parametres (colonne B, lignes 8 a 18) sont a saisir : tout le reste du tableau est calcule par formules et se met a jour automatiquement.</t>
         </is>
       </c>
     </row>

--- a/transactions/Recap_transaction_fonciere_appel_de_fonds.xlsx
+++ b/transactions/Recap_transaction_fonciere_appel_de_fonds.xlsx
@@ -166,12 +166,12 @@
     </comment>
     <comment ref="B16" authorId="0" shapeId="0">
       <text>
-        <t>Forfait plancher : si le pourcentage donne moins de 10 000 000 IDR, ce forfait s'applique a la place du pourcentage.</t>
+        <t>Forfait plancher : si le pourcentage donne moins de 20 000 000 IDR, ce forfait s'applique a la place du pourcentage.</t>
       </text>
     </comment>
     <comment ref="E28" authorId="0" shapeId="0">
       <text>
-        <t>MAX entre le pourcentage d'honoraires et le forfait minimum : si le pourcentage donne moins de 10 000 000 IDR, c'est le forfait qui s'applique.
+        <t>MAX entre le pourcentage d'honoraires et le forfait minimum : si le pourcentage donne moins de 20 000 000 IDR, c'est le forfait qui s'applique.
 La colonne des taux affiche le taux reellement supporte.</t>
       </text>
     </comment>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>10000000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="17">
@@ -769,7 +769,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Honoraires du notaire (1% du prix client, minimum 10 000 000 IDR)</t>
+          <t>Honoraires du notaire (1% du prix client, minimum 20 000 000 IDR)</t>
         </is>
       </c>
       <c r="D28" s="5">
@@ -928,7 +928,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Honoraires du notaire : le pourcentage s'applique sauf s'il donne moins que le forfait minimum de 10 000 000 IDR (B16), auquel cas le forfait est retenu (formule MAX en E28).</t>
+          <t>Honoraires du notaire : le pourcentage s'applique sauf s'il donne moins que le forfait minimum de 20 000 000 IDR (B16), auquel cas le forfait est retenu (formule MAX en E28).</t>
         </is>
       </c>
     </row>

--- a/transactions/Recap_transaction_fonciere_appel_de_fonds.xlsx
+++ b/transactions/Recap_transaction_fonciere_appel_de_fonds.xlsx
@@ -750,7 +750,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Taxes gouvernementales (5% du prix client)</t>
+          <t>Taxes gouvernementales (5% du prix officiel)</t>
         </is>
       </c>
       <c r="D27" s="5">
@@ -758,7 +758,7 @@
         <v/>
       </c>
       <c r="E27" s="4">
-        <f>E23*$B$14</f>
+        <f>E22*$B$14</f>
         <v/>
       </c>
       <c r="F27" s="3">
@@ -769,15 +769,15 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Honoraires du notaire (1% du prix client, minimum 20 000 000 IDR)</t>
+          <t>Honoraires du notaire (1% du prix officiel, minimum 20 000 000 IDR)</t>
         </is>
       </c>
       <c r="D28" s="5">
-        <f>IF(E23=0,0,E28/E23)</f>
+        <f>IF(E22=0,0,E28/E22)</f>
         <v/>
       </c>
       <c r="E28" s="4">
-        <f>MAX(E23*$B$15,$B$16)</f>
+        <f>MAX(E22*$B$15,$B$16)</f>
         <v/>
       </c>
       <c r="F28" s="3">
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="D29" s="5">
-        <f>IF(E23=0,0,E29/E23)</f>
+        <f>IF(E22=0,0,E29/E22)</f>
         <v/>
       </c>
       <c r="E29" s="4">
@@ -935,7 +935,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Ces taux sont appliques au prix client avec commission. Remplacer E23 par E22 dans les formules de frais si la base retenue est le prix vendeur.</t>
+          <t>Les frais de notaire portent sur le PRIX OFFICIEL, c'est-a-dire le prix vendeur declare a l'acte (ligne 22), et non sur le prix client commission comprise.</t>
         </is>
       </c>
     </row>
